--- a/sources/table_normalization/xlsx/environment-table28.xlsx
+++ b/sources/table_normalization/xlsx/environment-table28.xlsx
@@ -120,8 +120,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0.0%;[Red]\-0.0%"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0%;[Red]\-0.0%"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -337,32 +337,32 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -374,35 +374,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1213,38 +1213,38 @@
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="28" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="27" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:27" s="1" customFormat="1" ht="26.15" customHeight="1">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="34"/>
     </row>
     <row r="6" spans="1:27" ht="75" customHeight="1">
-      <c r="A6" s="34"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
@@ -1838,7 +1838,7 @@
       <c r="AA17" s="24"/>
     </row>
     <row r="18" spans="1:27" ht="30" customHeight="1">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="30" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="15">
